--- a/basedatos_partidas/salida/descompuestos/09.07.01.020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/09.07.01.020.xlsx
@@ -558,10 +558,10 @@
         <v>1.05</v>
       </c>
       <c r="G10" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>10.29</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="11">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12.08</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="14">
@@ -795,10 +795,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>15.47</v>
+        <v>16.73</v>
       </c>
       <c r="H23" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="24">
@@ -814,7 +814,7 @@
       </c>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="5" t="n">
-        <v>15.62</v>
+        <v>16.9</v>
       </c>
     </row>
   </sheetData>
